--- a/assets/constructions/examples/ctd_arb_extension.xlsx
+++ b/assets/constructions/examples/ctd_arb_extension.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG6"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,28 +594,44 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C8-390.140-50120</t>
+          <t>A101M.0.63.120.63</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>WALTER</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>80</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>80</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -625,9 +641,7 @@
       <c r="O2" t="n">
         <v>120</v>
       </c>
-      <c r="P2" t="n">
-        <v>221.75</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
@@ -645,12 +659,12 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>DIN_69871:SK50A</t>
+          <t>WALTER_NCT63</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>ISO_26623:80</t>
+          <t>WALTER_NCT63</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr"/>
@@ -661,108 +675,104 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2022 / www.coromant.sandvik.com</t>
-        </is>
-      </c>
+          <t>2012 / WALTER Оснастка</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VER20-M26</t>
+          <t>A101M.0.80.100.80</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DEREK</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Удлинители к патронам VER для синхронизированного резьбонарезания</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>25</v>
-      </c>
+          <t>WALTER</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
-        <v>34</v>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>26</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>51.5</v>
-      </c>
+      <c r="O3" t="n">
+        <v>100</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>ATTACHMENT</t>
+          <t>COLLET</t>
         </is>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>DER_VER:20</t>
+          <t>WALTER_NCT80</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>ER20-SQ</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>DER_VER20</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>DEREK</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+          <t>WALTER_NCT80</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="b">
+        <v>0</v>
+      </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>0.2</v>
+        <v>3.6</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
-        </is>
-      </c>
+          <t>2012 / WALTER Оснастка</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C25-ER20-150</t>
+          <t>DSF12-D3-55-2.25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -772,19 +782,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Цанговые удлинители ER</t>
+          <t>Удлинители с термозажимом DSF</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>34</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>7.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>12</v>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
         <v>42</v>
@@ -793,10 +805,10 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>192</v>
+        <v>55</v>
       </c>
       <c r="P4" t="n">
-        <v>192</v>
+        <v>55</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -804,28 +816,28 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>COLLET</t>
         </is>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>HA-25</t>
+          <t>DER_DSF:12</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>ER20</t>
+          <t>HA-3</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>HA-20</t>
+          <t>HA-3</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -837,7 +849,7 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>0.55</v>
+        <v>0.2</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -846,58 +858,86 @@
         <is>
           <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
         </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>8808.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A101M.0.63.120.63</t>
+          <t>NC25-ER25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WALTER</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" t="n">
+        <v>42</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>41</v>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>120</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
+        <v>106</v>
+      </c>
+      <c r="P5" t="n">
+        <v>106</v>
+      </c>
       <c r="Q5" t="n">
         <v>1</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>COLLET</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>WALTER_NCT63</t>
+          <t>HB-25</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>WALTER_NCT63</t>
+          <t>ER25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr"/>
@@ -908,21 +948,27 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>2.7</v>
+        <v>0.55</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2012 / WALTER Оснастка</t>
-        </is>
-      </c>
+          <t>2021/YG1-TOOLING</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C16-ER11M-150</t>
+          <t>C20-SF6-160</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -932,31 +978,31 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Цанговые удлинители ER (тип M)</t>
+          <t>Удлинители с темозажимом SF</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>25</v>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="P6" t="n">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -964,7 +1010,7 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
@@ -975,17 +1021,17 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>HA-16</t>
+          <t>HA-20</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>ER11</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>HA-11</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -997,7 +1043,7 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
-        <v>0.22</v>
+        <v>0.42</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1006,6 +1052,20 @@
         <is>
           <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
         </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>116.39</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>9540.940000000001</v>
       </c>
     </row>
   </sheetData>
